--- a/data/trans_orig/P02E$contratada-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007 (tasa de respuesta: 96,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54795</t>
+          <t>54414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>62915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91503</t>
+          <t>90878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102123</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150568</t>
+          <t>150503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163111</t>
+          <t>163881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16048</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59422</t>
+          <t>59369</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>67995</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100794</t>
+          <t>100394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119576</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>165098</t>
+          <t>165763</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185759</t>
+          <t>185883</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29143</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>34880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55217</t>
+          <t>54950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65702</t>
+          <t>65848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>92445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103179</t>
+          <t>103087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152524</t>
+          <t>151026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166826</t>
+          <t>166694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69156</t>
+          <t>69875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80797</t>
+          <t>80637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96282</t>
+          <t>96696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110075</t>
+          <t>110399</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171312</t>
+          <t>170561</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188462</t>
+          <t>188276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29967</t>
+          <t>30688</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>40531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50683</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>64394</t>
+          <t>63859</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77775</t>
+          <t>77771</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45333</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57453</t>
+          <t>57554</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56510</t>
+          <t>56804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67161</t>
+          <t>66958</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108418</t>
+          <t>107560</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122367</t>
+          <t>121854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92050</t>
+          <t>91090</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104819</t>
+          <t>104484</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>214480</t>
+          <t>213645</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>221471</t>
+          <t>221475</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>309796</t>
+          <t>310260</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>324417</t>
+          <t>324936</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>21877</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>110887</t>
+          <t>111305</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>126554</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>170616</t>
+          <t>170904</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>187182</t>
+          <t>187273</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>288232</t>
+          <t>287672</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>311629</t>
+          <t>311367</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12845</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31301</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>41980</t>
+          <t>41571</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>546033</t>
+          <t>542866</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>577409</t>
+          <t>575356</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>902148</t>
+          <t>904399</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>938991</t>
+          <t>938538</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1458464</t>
+          <t>1459284</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1506307</t>
+          <t>1507798</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>48783</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>77212</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>93071</t>
+          <t>92870</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>134732</t>
+          <t>134030</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24446</t>
+          <t>24345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70107</t>
+          <t>69447</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82458</t>
+          <t>82555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110545</t>
+          <t>109597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128683</t>
+          <t>128793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185559</t>
+          <t>186147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208568</t>
+          <t>208497</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12707</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112174</t>
+          <t>114298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125257</t>
+          <t>125321</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>188936</t>
+          <t>188897</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203155</t>
+          <t>203938</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>306907</t>
+          <t>308406</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>326312</t>
+          <t>326434</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81624</t>
+          <t>81155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91310</t>
+          <t>90690</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115357</t>
+          <t>115873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130632</t>
+          <t>131525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>202829</t>
+          <t>201620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219793</t>
+          <t>220025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25293</t>
+          <t>27238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87233</t>
+          <t>85811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103182</t>
+          <t>103438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141885</t>
+          <t>141136</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161052</t>
+          <t>161249</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234668</t>
+          <t>236416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260267</t>
+          <t>261471</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28849</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41768</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6829,47 +6829,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>8233</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>15709</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>5,38%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>8233</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>3248</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>15319</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50685</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73858</t>
+          <t>74165</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86461</t>
+          <t>86438</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>116627</t>
+          <t>117462</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>134619</t>
+          <t>135477</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7320,12 +7320,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72049</t>
+          <t>71625</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80228</t>
+          <t>80202</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97846</t>
+          <t>97540</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108111</t>
+          <t>107294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173610</t>
+          <t>173551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>187157</t>
+          <t>186408</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>187917</t>
+          <t>188092</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>204642</t>
+          <t>204669</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>259540</t>
+          <t>259052</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>274776</t>
+          <t>274516</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>453867</t>
+          <t>454004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>475754</t>
+          <t>476611</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16211</t>
+          <t>17012</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>188100</t>
+          <t>189063</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>203223</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>331053</t>
+          <t>330691</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>347132</t>
+          <t>347075</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>525722</t>
+          <t>525014</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>547367</t>
+          <t>546790</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>19437</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>61688</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>881615</t>
+          <t>880605</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>916099</t>
+          <t>917356</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1366090</t>
+          <t>1367614</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1411974</t>
+          <t>1410901</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2260750</t>
+          <t>2263198</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2318630</t>
+          <t>2319630</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>37619</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>63294</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>100977</t>
+          <t>98066</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>110604</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>158601</t>
+          <t>156063</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9074,12 +9074,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>30853</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>50094</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016 (tasa de respuesta: 93,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68220</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65854</t>
+          <t>65330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82517</t>
+          <t>82408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128323</t>
+          <t>127911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148291</t>
+          <t>148367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37240</t>
+          <t>37496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75743</t>
+          <t>75862</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>114586</t>
+          <t>114968</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127902</t>
+          <t>127960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>183341</t>
+          <t>185012</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>200985</t>
+          <t>201717</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -10207,12 +10207,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10277,12 +10277,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50203</t>
+          <t>50526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58125</t>
+          <t>58075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62954</t>
+          <t>62765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75254</t>
+          <t>75016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117221</t>
+          <t>116673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131612</t>
+          <t>131196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>15413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>48283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57178</t>
+          <t>57288</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99404</t>
+          <t>99833</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112770</t>
+          <t>113164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151769</t>
+          <t>152060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>167874</t>
+          <t>167198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61514</t>
+          <t>60733</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70881</t>
+          <t>71400</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70644</t>
+          <t>70051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>81155</t>
+          <t>81022</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>136405</t>
+          <t>136764</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>150435</t>
+          <t>150148</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -11575,12 +11575,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52937</t>
+          <t>52587</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61646</t>
+          <t>61447</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60043</t>
+          <t>60621</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68834</t>
+          <t>68891</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117518</t>
+          <t>117475</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>129497</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>103422</t>
+          <t>104668</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116978</t>
+          <t>117049</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>161079</t>
+          <t>161002</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>182814</t>
+          <t>182271</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>270615</t>
+          <t>270378</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296240</t>
+          <t>295999</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40479</t>
+          <t>38824</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>46755</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20912</t>
+          <t>20931</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>200513</t>
+          <t>199078</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>216412</t>
+          <t>215568</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>269758</t>
+          <t>269987</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>294147</t>
+          <t>294259</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>475622</t>
+          <t>477932</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>505046</t>
+          <t>505109</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t>40310</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28930</t>
+          <t>29247</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55179</t>
+          <t>52933</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>28417</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>54874</t>
+          <t>55725</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>675488</t>
+          <t>675867</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>705880</t>
+          <t>707739</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>950221</t>
+          <t>951264</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>995994</t>
+          <t>995468</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1638097</t>
+          <t>1636825</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1689040</t>
+          <t>1689541</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>27861</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>85700</t>
+          <t>86790</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>126184</t>
+          <t>125425</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>121619</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>169745</t>
+          <t>171046</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>32176</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P02E$contratada-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54414</t>
+          <t>54889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62915</t>
+          <t>62952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90878</t>
+          <t>92090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102093</t>
+          <t>102133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150503</t>
+          <t>150302</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163881</t>
+          <t>163152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59369</t>
+          <t>59012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67995</t>
+          <t>67996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>100874</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119840</t>
+          <t>119706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>165763</t>
+          <t>165484</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185883</t>
+          <t>184494</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>29844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34880</t>
+          <t>34441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54950</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65848</t>
+          <t>65733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92445</t>
+          <t>93100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103087</t>
+          <t>103164</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151026</t>
+          <t>151276</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166694</t>
+          <t>166130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69875</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80637</t>
+          <t>80700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96696</t>
+          <t>96732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110399</t>
+          <t>109682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>170561</t>
+          <t>170385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188276</t>
+          <t>187733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30688</t>
+          <t>29991</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40531</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50490</t>
+          <t>49884</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>63859</t>
+          <t>64262</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77771</t>
+          <t>77359</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46534</t>
+          <t>46086</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57554</t>
+          <t>57447</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56804</t>
+          <t>56433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66958</t>
+          <t>66948</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107560</t>
+          <t>107809</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121854</t>
+          <t>122102</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>91090</t>
+          <t>91376</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104484</t>
+          <t>104586</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>213645</t>
+          <t>214328</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>221475</t>
+          <t>221467</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>310260</t>
+          <t>310428</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>324936</t>
+          <t>325242</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21877</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>111305</t>
+          <t>110694</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>126554</t>
+          <t>126567</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>170904</t>
+          <t>170645</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>187273</t>
+          <t>187186</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>287672</t>
+          <t>287988</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>311367</t>
+          <t>310519</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19702</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>31790</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>41571</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>542866</t>
+          <t>545566</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>575356</t>
+          <t>576200</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>904399</t>
+          <t>903129</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>938538</t>
+          <t>938878</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1459284</t>
+          <t>1458314</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1507798</t>
+          <t>1506480</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>66471</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>48783</t>
+          <t>48958</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>77764</t>
+          <t>79429</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>92870</t>
+          <t>92771</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>134030</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19877</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69447</t>
+          <t>70516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82555</t>
+          <t>82709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109597</t>
+          <t>110389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128793</t>
+          <t>128079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186147</t>
+          <t>186849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208497</t>
+          <t>208851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114298</t>
+          <t>114436</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125321</t>
+          <t>125152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>188897</t>
+          <t>189011</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203938</t>
+          <t>203855</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>308406</t>
+          <t>307350</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>326434</t>
+          <t>326565</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81155</t>
+          <t>80857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90690</t>
+          <t>91308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115873</t>
+          <t>116046</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131525</t>
+          <t>131242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>201620</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220025</t>
+          <t>220222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85811</t>
+          <t>87998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103438</t>
+          <t>103852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141136</t>
+          <t>141177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161249</t>
+          <t>161315</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236416</t>
+          <t>235921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>261471</t>
+          <t>260924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20837</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>29608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41369</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39141</t>
+          <t>37769</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50742</t>
+          <t>50813</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74165</t>
+          <t>73909</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86438</t>
+          <t>86486</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117462</t>
+          <t>117278</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135477</t>
+          <t>134225</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>21379</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7320,12 +7320,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71625</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80202</t>
+          <t>80272</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>98265</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107294</t>
+          <t>108117</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173551</t>
+          <t>173830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186408</t>
+          <t>186569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -7726,12 +7726,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>188092</t>
+          <t>187770</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>204669</t>
+          <t>205065</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>259052</t>
+          <t>259064</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>274516</t>
+          <t>274528</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>454004</t>
+          <t>455097</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>476611</t>
+          <t>476474</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>29807</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>189063</t>
+          <t>188467</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>203223</t>
+          <t>202626</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>330691</t>
+          <t>330664</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>347075</t>
+          <t>347268</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>525014</t>
+          <t>526906</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>546790</t>
+          <t>547319</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>20563</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>41013</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>32198</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>61688</t>
+          <t>61828</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>880605</t>
+          <t>881128</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>917356</t>
+          <t>917470</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1367614</t>
+          <t>1366515</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1410901</t>
+          <t>1409518</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2263198</t>
+          <t>2259547</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2319630</t>
+          <t>2316987</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>63874</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>111033</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>156063</t>
+          <t>156376</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9074,12 +9074,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>50094</t>
+          <t>49172</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>56836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68992</t>
+          <t>69081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65330</t>
+          <t>65849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82408</t>
+          <t>82648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127911</t>
+          <t>127451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148367</t>
+          <t>148666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37496</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64941</t>
+          <t>65130</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75862</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>114968</t>
+          <t>114256</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127960</t>
+          <t>127994</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>185012</t>
+          <t>185604</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>201717</t>
+          <t>202251</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -10207,12 +10207,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10277,12 +10277,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50526</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58075</t>
+          <t>58121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62765</t>
+          <t>62169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75016</t>
+          <t>74639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116673</t>
+          <t>117054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131196</t>
+          <t>131000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48283</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57288</t>
+          <t>57234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99833</t>
+          <t>99830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113164</t>
+          <t>112528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152060</t>
+          <t>152849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>167198</t>
+          <t>167546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60733</t>
+          <t>61585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71400</t>
+          <t>70795</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70051</t>
+          <t>70136</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>81022</t>
+          <t>81132</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>136764</t>
+          <t>137227</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>150148</t>
+          <t>150257</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11615,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52587</t>
+          <t>52783</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61447</t>
+          <t>61670</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60621</t>
+          <t>60437</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68891</t>
+          <t>68804</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117475</t>
+          <t>117686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>129558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104668</t>
+          <t>104100</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117049</t>
+          <t>117054</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>161002</t>
+          <t>162145</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>182271</t>
+          <t>183376</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>270378</t>
+          <t>271785</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>295999</t>
+          <t>297302</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38824</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23588</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>45633</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>199078</t>
+          <t>199825</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>215568</t>
+          <t>216262</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>269987</t>
+          <t>269150</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>294259</t>
+          <t>293075</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>477932</t>
+          <t>476269</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>505109</t>
+          <t>504515</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>40310</t>
+          <t>41241</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>30152</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>54693</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>55725</t>
+          <t>54461</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>675867</t>
+          <t>674813</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>707739</t>
+          <t>705713</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>951264</t>
+          <t>950051</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>995468</t>
+          <t>994923</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1636825</t>
+          <t>1636538</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1689541</t>
+          <t>1691819</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>52759</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>86790</t>
+          <t>85011</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>125425</t>
+          <t>125404</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>122174</t>
+          <t>122813</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>171046</t>
+          <t>167237</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>32692</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
